--- a/public/templates/examples/A-003-MasterAssetInventory-EXAMPLE-S.xlsx
+++ b/public/templates/examples/A-003-MasterAssetInventory-EXAMPLE-S.xlsx
@@ -19,7 +19,7 @@
   <numFmts count="0"/>
   <fonts count="8">
     <font>
-      <name val="Calibri"/>
+      <name val="Aptos"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
@@ -224,12 +224,12 @@
 <wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
-      <col>0</col>
+      <col>10</col>
       <colOff>0</colOff>
       <row>0</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="552450" cy="552450"/>
+    <ext cx="857250" cy="857250"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -368,7 +368,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Aptos"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -402,7 +402,7 @@
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Aptos"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>

--- a/public/templates/examples/A-003-MasterAssetInventory-EXAMPLE-S.xlsx
+++ b/public/templates/examples/A-003-MasterAssetInventory-EXAMPLE-S.xlsx
@@ -4,19 +4,24 @@
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Register" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">Register!$11:$11</definedName>
+  </definedNames>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+  </numFmts>
   <fonts count="8">
     <font>
       <name val="Aptos"/>
@@ -107,7 +112,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -142,6 +147,12 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf applyNumberFormat="1" numFmtId="164" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf applyNumberFormat="1" numFmtId="164" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -612,7 +623,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:K54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -815,7 +826,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="19.5" customHeight="1">
+    <row r="12" ht="34.7" customHeight="1">
       <c r="A12" s="8" t="inlineStr">
         <is>
           <t>AST-001</t>
@@ -861,18 +872,14 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="J12" s="8" t="inlineStr">
-        <is>
-          <t>2026-01-12</t>
-        </is>
-      </c>
-      <c r="K12" s="8" t="inlineStr">
-        <is>
-          <t>2026-04-12</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="19.5" customHeight="1">
+      <c r="J12" s="14">
+        <v>46034</v>
+      </c>
+      <c r="K12" s="14">
+        <v>46124</v>
+      </c>
+    </row>
+    <row r="13" ht="34.7" customHeight="1">
       <c r="A13" s="8" t="inlineStr">
         <is>
           <t>AST-002</t>
@@ -918,18 +925,14 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="J13" s="8" t="inlineStr">
-        <is>
-          <t>2026-01-12</t>
-        </is>
-      </c>
-      <c r="K13" s="8" t="inlineStr">
-        <is>
-          <t>2026-04-12</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="19.5" customHeight="1">
+      <c r="J13" s="14">
+        <v>46034</v>
+      </c>
+      <c r="K13" s="14">
+        <v>46124</v>
+      </c>
+    </row>
+    <row r="14" ht="34.7" customHeight="1">
       <c r="A14" s="8" t="inlineStr">
         <is>
           <t>AST-003</t>
@@ -975,18 +978,14 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="J14" s="8" t="inlineStr">
-        <is>
-          <t>2026-01-12</t>
-        </is>
-      </c>
-      <c r="K14" s="8" t="inlineStr">
-        <is>
-          <t>2026-04-12</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="19.5" customHeight="1">
+      <c r="J14" s="14">
+        <v>46034</v>
+      </c>
+      <c r="K14" s="14">
+        <v>46124</v>
+      </c>
+    </row>
+    <row r="15" ht="34.7" customHeight="1">
       <c r="A15" s="8" t="inlineStr">
         <is>
           <t>AST-004</t>
@@ -1032,18 +1031,14 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="J15" s="8" t="inlineStr">
-        <is>
-          <t>2026-01-12</t>
-        </is>
-      </c>
-      <c r="K15" s="8" t="inlineStr">
-        <is>
-          <t>2026-04-12</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="19.5" customHeight="1">
+      <c r="J15" s="14">
+        <v>46034</v>
+      </c>
+      <c r="K15" s="14">
+        <v>46124</v>
+      </c>
+    </row>
+    <row r="16" ht="34.7" customHeight="1">
       <c r="A16" s="8" t="inlineStr">
         <is>
           <t>AST-005</t>
@@ -1089,18 +1084,14 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="J16" s="8" t="inlineStr">
-        <is>
-          <t>2026-01-12</t>
-        </is>
-      </c>
-      <c r="K16" s="8" t="inlineStr">
-        <is>
-          <t>2026-04-12</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="19.5" customHeight="1">
+      <c r="J16" s="14">
+        <v>46034</v>
+      </c>
+      <c r="K16" s="14">
+        <v>46124</v>
+      </c>
+    </row>
+    <row r="17" ht="34.7" customHeight="1">
       <c r="A17" s="8" t="inlineStr">
         <is>
           <t>AST-006</t>
@@ -1146,18 +1137,14 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="J17" s="8" t="inlineStr">
-        <is>
-          <t>2026-01-12</t>
-        </is>
-      </c>
-      <c r="K17" s="8" t="inlineStr">
-        <is>
-          <t>2026-04-12</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="19.5" customHeight="1">
+      <c r="J17" s="14">
+        <v>46034</v>
+      </c>
+      <c r="K17" s="14">
+        <v>46124</v>
+      </c>
+    </row>
+    <row r="18" ht="34.7" customHeight="1">
       <c r="A18" s="8" t="inlineStr">
         <is>
           <t>AST-007</t>
@@ -1203,18 +1190,14 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="J18" s="8" t="inlineStr">
-        <is>
-          <t>2026-01-12</t>
-        </is>
-      </c>
-      <c r="K18" s="8" t="inlineStr">
-        <is>
-          <t>2026-04-12</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="19.5" customHeight="1">
+      <c r="J18" s="14">
+        <v>46034</v>
+      </c>
+      <c r="K18" s="14">
+        <v>46124</v>
+      </c>
+    </row>
+    <row r="19" ht="34.7" customHeight="1">
       <c r="A19" s="8" t="inlineStr">
         <is>
           <t>AST-008</t>
@@ -1260,18 +1243,14 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="J19" s="8" t="inlineStr">
-        <is>
-          <t>2026-01-12</t>
-        </is>
-      </c>
-      <c r="K19" s="8" t="inlineStr">
-        <is>
-          <t>2026-04-12</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="19.5" customHeight="1">
+      <c r="J19" s="14">
+        <v>46034</v>
+      </c>
+      <c r="K19" s="14">
+        <v>46124</v>
+      </c>
+    </row>
+    <row r="20" ht="34.7" customHeight="1">
       <c r="A20" s="8" t="inlineStr">
         <is>
           <t>AST-009</t>
@@ -1317,18 +1296,14 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="J20" s="8" t="inlineStr">
-        <is>
-          <t>2026-01-12</t>
-        </is>
-      </c>
-      <c r="K20" s="8" t="inlineStr">
-        <is>
-          <t>2026-04-12</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="19.5" customHeight="1">
+      <c r="J20" s="14">
+        <v>46034</v>
+      </c>
+      <c r="K20" s="14">
+        <v>46124</v>
+      </c>
+    </row>
+    <row r="21" ht="34.7" customHeight="1">
       <c r="A21" s="8" t="inlineStr">
         <is>
           <t>AST-010</t>
@@ -1374,18 +1349,14 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="J21" s="8" t="inlineStr">
-        <is>
-          <t>2026-01-12</t>
-        </is>
-      </c>
-      <c r="K21" s="8" t="inlineStr">
-        <is>
-          <t>2026-04-12</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="19.5" customHeight="1">
+      <c r="J21" s="14">
+        <v>46034</v>
+      </c>
+      <c r="K21" s="14">
+        <v>46124</v>
+      </c>
+    </row>
+    <row r="22" ht="34.7" customHeight="1">
       <c r="A22" s="8" t="inlineStr">
         <is>
           <t>AST-011</t>
@@ -1431,15 +1402,11 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="J22" s="8" t="inlineStr">
-        <is>
-          <t>2026-01-12</t>
-        </is>
-      </c>
-      <c r="K22" s="8" t="inlineStr">
-        <is>
-          <t>2026-04-12</t>
-        </is>
+      <c r="J22" s="14">
+        <v>46034</v>
+      </c>
+      <c r="K22" s="14">
+        <v>46087</v>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1"/>
@@ -1487,7 +1454,7 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="19.5" customHeight="1">
+    <row r="26" ht="34.7" customHeight="1">
       <c r="A26" s="8" t="inlineStr">
         <is>
           <t>AST-001</t>
@@ -1513,10 +1480,8 @@
           <t>EDR agent (managed)</t>
         </is>
       </c>
-      <c r="F26" s="8" t="inlineStr">
-        <is>
-          <t>2026-01-12</t>
-        </is>
+      <c r="F26" s="14">
+        <v>46034</v>
       </c>
       <c r="G26" s="8" t="inlineStr">
         <is>
@@ -1524,7 +1489,7 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="19.5" customHeight="1">
+    <row r="27" ht="50.5" customHeight="1">
       <c r="A27" s="8" t="inlineStr">
         <is>
           <t>AST-002</t>
@@ -1550,10 +1515,8 @@
           <t>EDR agent (managed)</t>
         </is>
       </c>
-      <c r="F27" s="8" t="inlineStr">
-        <is>
-          <t>2026-01-12</t>
-        </is>
+      <c r="F27" s="14">
+        <v>46034</v>
       </c>
       <c r="G27" s="8" t="inlineStr">
         <is>
@@ -1561,7 +1524,7 @@
         </is>
       </c>
     </row>
-    <row r="28" ht="19.5" customHeight="1">
+    <row r="28" ht="50.5" customHeight="1">
       <c r="A28" s="8" t="inlineStr">
         <is>
           <t>AST-003</t>
@@ -1587,10 +1550,8 @@
           <t>EDR agent (managed)</t>
         </is>
       </c>
-      <c r="F28" s="8" t="inlineStr">
-        <is>
-          <t>2026-01-12</t>
-        </is>
+      <c r="F28" s="14">
+        <v>46034</v>
       </c>
       <c r="G28" s="8" t="inlineStr">
         <is>
@@ -1598,7 +1559,7 @@
         </is>
       </c>
     </row>
-    <row r="29" ht="19.5" customHeight="1">
+    <row r="29" ht="50.5" customHeight="1">
       <c r="A29" s="8" t="inlineStr">
         <is>
           <t>AST-004</t>
@@ -1624,10 +1585,8 @@
           <t>EDR agent (managed)</t>
         </is>
       </c>
-      <c r="F29" s="8" t="inlineStr">
-        <is>
-          <t>2026-01-11</t>
-        </is>
+      <c r="F29" s="14">
+        <v>46033</v>
       </c>
       <c r="G29" s="8" t="inlineStr">
         <is>
@@ -1635,7 +1594,7 @@
         </is>
       </c>
     </row>
-    <row r="30" ht="19.5" customHeight="1">
+    <row r="30" ht="50.5" customHeight="1">
       <c r="A30" s="8" t="inlineStr">
         <is>
           <t>AST-011</t>
@@ -1661,10 +1620,8 @@
           <t>EDR agent (managed)</t>
         </is>
       </c>
-      <c r="F30" s="8" t="inlineStr">
-        <is>
-          <t>2026-01-10</t>
-        </is>
+      <c r="F30" s="14">
+        <v>46032</v>
       </c>
       <c r="G30" s="8" t="inlineStr">
         <is>
@@ -1676,7 +1633,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" s="6" t="inlineStr">
         <is>
-          <t>Summary</t>
+          <t>Summary (as of 2026-03-07)</t>
         </is>
       </c>
     </row>
@@ -1688,7 +1645,6 @@
       </c>
       <c r="C33" s="10">
         <f>COUNTA(A12:A22)</f>
-        <v/>
       </c>
     </row>
     <row r="34" ht="15" customHeight="1">
@@ -1699,7 +1655,6 @@
       </c>
       <c r="C34" s="10">
         <f>COUNTIF(I12:I22,"Active")</f>
-        <v/>
       </c>
     </row>
     <row r="35" ht="15" customHeight="1">
@@ -1710,7 +1665,6 @@
       </c>
       <c r="C35" s="10">
         <f>COUNTIF(I12:I22,"Under Review")</f>
-        <v/>
       </c>
     </row>
     <row r="36" ht="15" customHeight="1">
@@ -1721,7 +1675,6 @@
       </c>
       <c r="C36" s="10">
         <f>COUNTIF(I12:I22,"Retired")</f>
-        <v/>
       </c>
     </row>
     <row r="37" ht="15" customHeight="1">
@@ -1732,7 +1685,6 @@
       </c>
       <c r="C37" s="10">
         <f>COUNTIF(I12:I22,"Decommissioned")</f>
-        <v/>
       </c>
     </row>
     <row r="38" ht="15" customHeight="1">
@@ -1742,8 +1694,7 @@
         </is>
       </c>
       <c r="C38" s="10">
-        <f>COUNTIF(K12:K22,"&lt;"&amp;TODAY())</f>
-        <v/>
+        <f>COUNTIF(K12:K22,"&lt;"&amp;DATE(2026,3,7))</f>
       </c>
     </row>
     <row r="39" ht="15" customHeight="1"/>
@@ -1829,10 +1780,8 @@
           <t>Tracy Holloway</t>
         </is>
       </c>
-      <c r="D49" s="12" t="inlineStr">
-        <is>
-          <t>2026-01-15</t>
-        </is>
+      <c r="D49" s="15">
+        <v>46037</v>
       </c>
     </row>
     <row r="50" ht="26" customHeight="1">
@@ -1851,10 +1800,8 @@
           <t>(on file)</t>
         </is>
       </c>
-      <c r="D50" s="12" t="inlineStr">
-        <is>
-          <t>2026-01-15</t>
-        </is>
+      <c r="D50" s="15">
+        <v>46037</v>
       </c>
     </row>
     <row r="51" ht="15" customHeight="1"/>
@@ -1887,16 +1834,14 @@
         </is>
       </c>
     </row>
-    <row r="54" ht="17" customHeight="1">
+    <row r="54" ht="34.7" customHeight="1">
       <c r="A54" s="8" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="B54" s="8" t="inlineStr">
-        <is>
-          <t>2026-01-15</t>
-        </is>
+      <c r="B54" s="14">
+        <v>46037</v>
       </c>
       <c r="C54" s="8" t="inlineStr">
         <is>
@@ -1934,7 +1879,8 @@
     <mergeCell ref="C4:K4"/>
     <mergeCell ref="A40:K40"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="1" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>